--- a/sheets/대금율보/검수/잦은 육자백이.xlsx
+++ b/sheets/대금율보/검수/잦은 육자백이.xlsx
@@ -6477,32 +6477,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="158.96" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="158.96" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="158.96" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="158.96" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="158.96" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="158.96" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="158.96" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="158.96" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="26"/>
@@ -7080,7 +7080,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="158.96" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -7153,10 +7153,10 @@
       </c>
       <c r="U11" s="28"/>
     </row>
-    <row r="12">
+    <row r="12" ht="6.0" customHeight="true">
       <c r="A12" s="0"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="80.0" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="20" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
       <c r="T13" s="20"/>
       <c r="U13" s="20"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="158.96" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="158.96" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="158.96" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="158.96" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="158.96" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
@@ -7575,7 +7575,7 @@
       <c r="T18" s="21"/>
       <c r="U18" s="22"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="158.96" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
       <c r="T19" s="21"/>
       <c r="U19" s="23"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="158.96" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="158.96" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="158.96" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -7856,10 +7856,10 @@
       </c>
       <c r="U22" s="28"/>
     </row>
-    <row r="23">
+    <row r="23" ht="6.0" customHeight="true">
       <c r="A23" s="0"/>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="80.0" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="20" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
       <c r="T24" s="20"/>
       <c r="U24" s="20"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="158.96" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="158.96" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="23"/>
@@ -7993,7 +7993,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="158.96" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="158.96" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="26"/>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="158.96" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="158.96" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="23"/>
@@ -8163,7 +8163,7 @@
       <c r="T30" s="21"/>
       <c r="U30" s="23"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="158.96" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="23"/>
@@ -8210,7 +8210,7 @@
       <c r="T31" s="21"/>
       <c r="U31" s="23"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="158.96" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="26"/>
@@ -8246,7 +8246,7 @@
       <c r="T32" s="21"/>
       <c r="U32" s="26"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="158.96" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="28"/>
@@ -8304,7 +8304,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="11" max="16383" man="1"/>
     <brk id="22" max="16383" man="1"/>
